--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2020_biobio_provincial.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2020_biobio_provincial.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Bíobío</t>
+    <t xml:space="preserve">Bío-Bío</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 23:00</t>
+    <t xml:space="preserve">2026-10-05 05:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Biobio</t>
+    <t xml:space="preserve">Region de Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
